--- a/public/sap-reporting/expansion-150-downloads/EXT-MM18-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM18-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R79c77abb06c44a4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R95928db4cf2144e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Ra4700aff8a8e471d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R946d65fb7bb54be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rd4aa8a3ab61c49fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R494b7d6c50c7494c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -533,10 +533,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="P7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="Q7" s="2" t="str">
         <x:v>100.00</x:v>
@@ -593,10 +593,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="P8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="Q8" s="2" t="str">
         <x:v>125.00</x:v>
@@ -653,10 +653,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="P9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="Q9" s="2" t="str">
         <x:v>1.234,50</x:v>
@@ -715,10 +715,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="P10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="Q10" s="2" t="str">
         <x:v>175.00</x:v>
@@ -880,10 +880,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="P2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="str">
         <x:v>100.00</x:v>
@@ -940,10 +940,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="P3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="Q3" s="2" t="str">
         <x:v>125.00</x:v>
@@ -1000,10 +1000,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="P4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="Q4" s="2" t="str">
         <x:v>1.234,50</x:v>
@@ -1062,10 +1062,10 @@
         <x:v>EA</x:v>
       </x:c>
       <x:c r="O5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="P5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="Q5" s="2" t="str">
         <x:v>175.00</x:v>
@@ -1340,7 +1340,7 @@
         <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="63" customHeight="1">
+    <x:row r="13" ht="80" customHeight="1">
       <x:c r="A13" s="8" t="str">
         <x:v>12</x:v>
       </x:c>
@@ -1348,7 +1348,7 @@
         <x:v>Price Unit</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>Số đơn vị làm mẫu số của đơn giá</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="63" customHeight="1">
@@ -1400,7 +1400,7 @@
         <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="63" customHeight="1">
+    <x:row r="16" ht="80" customHeight="1">
       <x:c r="A16" s="8" t="str">
         <x:v>15</x:v>
       </x:c>
@@ -1408,7 +1408,7 @@
         <x:v>Conversion Numerator</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Conversion Numerator. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1417,10 +1417,10 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="63" customHeight="1">
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="80" customHeight="1">
       <x:c r="A17" s="8" t="str">
         <x:v>16</x:v>
       </x:c>
@@ -1428,7 +1428,7 @@
         <x:v>Conversion Denominator</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Conversion Denominator. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1437,7 +1437,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="80" customHeight="1">
